--- a/www/download/COUNTRY.CZE.zdW13.xlsx
+++ b/www/download/COUNTRY.CZE.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>República Tcheca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.5322375111802</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27.1370408253621</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.5159153924822</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.1646826403424</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.518468120635</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.431975719047</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.008361220193</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.5839042490637</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.1610815462506</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.6476028977032</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.9291690489315</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5580866760044</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2224473160373</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.9492103310518</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.9405056976826</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.148</t>
+          <t>2.01603590357203</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.195</t>
+          <t>1.12416761594042</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.205</t>
+          <t>1.35403188994062</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>1.29188595315727</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.949</t>
+          <t>1.29615204210999</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>1.39137348442416</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.963</t>
+          <t>1.15614460168806</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.991</t>
+          <t>1.08007542907705</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.923</t>
+          <t>1.07985256906632</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.745475644130422</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.992</t>
+          <t>0.691182866627557</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.088</t>
+          <t>0.746297846440201</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5.224</t>
+          <t>0.701678150927227</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5.349</t>
+          <t>0.692617999031871</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.232</t>
+          <t>0.929102196064292</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.436</t>
+          <t>4.60267458102713</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>2.97375022284967</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.419</t>
+          <t>3.38539781006387</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>3.21831763896239</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>3.24738564974302</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.083</t>
+          <t>3.40267787561567</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.099</t>
+          <t>3.05825502300437</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>2.92592812465366</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.981</t>
+          <t>2.54926279614415</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.011</t>
+          <t>2.30940597564375</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>2.20908593635494</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>2.33880301626224</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.279</t>
+          <t>2.27718509304788</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>2.13692024753459</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.254</t>
+          <t>2.62303727658443</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10385.389</t>
+          <t>6.75820983129756</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10466.783</t>
+          <t>4.49592790536796</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10506.601</t>
+          <t>5.07822910245806</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10374.742</t>
+          <t>4.82489411389685</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10183.985</t>
+          <t>4.84938181454236</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10157.388</t>
+          <t>4.93858108148444</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9751.944</t>
+          <t>4.60137736188811</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9700.054</t>
+          <t>4.24915184091539</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9578.514</t>
+          <t>2.31234059738105</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9651.583</t>
+          <t>3.42961240311042</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9808.906</t>
+          <t>3.28305733566755</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9974.58</t>
+          <t>3.45217541678767</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10175.114</t>
+          <t>3.12070642623639</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>10460.522</t>
+          <t>2.84412635284571</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10103.591</t>
+          <t>3.49800516649456</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8581.482</t>
+          <t>11896828949.7572</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8594.152</t>
+          <t>12008962189.3661</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8546.09</t>
+          <t>12059733358.6253</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8336.71</t>
+          <t>11871525933.7446</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8137.807</t>
+          <t>11452828616.6649</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8094.805</t>
+          <t>11082359205.2714</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7714.352</t>
+          <t>11206420324.0133</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7569.647</t>
+          <t>11304352239.2366</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7358.729</t>
+          <t>11288292689.9529</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7481.786</t>
+          <t>11637768197.7029</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7685.812</t>
+          <t>11690997664.0313</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7832.395</t>
+          <t>12611501825.7834</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>8030.064</t>
+          <t>13135858935.1004</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>8156.526</t>
+          <t>13778287726.2227</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>8002.884</t>
+          <t>11525255767.9424</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>1642916308.35956</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>2322328484.79243</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>2091604804.50066</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>2118632903.62114</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>2065185859.26022</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>1990646451.15151</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>2072515160.33446</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>2116363979.26062</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>2281627491.60717</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>2512179195.83279</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2674179633.89609</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>2630476481.1758</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>2757773120.58789</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>2923652050.53211</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>2517701642.9049</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>3025495.44736765</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>2777531.35584285</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>2966886.52192307</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>2791148.28809635</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>2837966.65974445</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>76.12</t>
+          <t>2841482.48487325</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.98</t>
+          <t>2620909.73082346</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>2262267.28594055</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>1836469.6151672</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>1552453.34777911</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>1436380.06708275</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.92</t>
+          <t>1314356.53055468</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>1098316.90127007</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>940072.115632993</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>1010671.31872134</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>55167.9482257242</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>56279.4253383693</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>55765.5278437432</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>54167.4775688337</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>54206.6474530312</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>54246.7569686002</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>50614.9407015455</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>50856.449973337</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>53345.8645435553</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>58890.2676660114</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>63760.038652336</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>67397.0626114771</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>77142.8882038948</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>86275.4628519997</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>75812.6004287191</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>102508.652875926</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>104215.494456868</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>104320.33166935</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>101656.348709783</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>102010.07501376</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>100342.621608906</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>98541.6602548556</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>101572.659998042</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>108734.79491259</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>123301.521210254</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>132667.189255719</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>149404.498487563</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>175339.153751341</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>201352.35574172</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>157008.077930365</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>4.22332267099386</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>2.70066166620186</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>3.08590092239735</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>2.93494785517161</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>80.48</t>
+          <t>2.94047197423435</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>80.62</t>
+          <t>3.0664202301305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>2.72221740407199</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>80.98</t>
+          <t>2.57672265932468</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>2.22521052497336</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>1.97820554059631</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>81.68</t>
+          <t>1.87408216807123</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>81.33</t>
+          <t>1.9775575094665</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>81.21</t>
+          <t>1.9117928302558</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>1.78984156083672</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>79.99</t>
+          <t>2.17864662302988</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26.5322375111802</t>
+          <t>370.397176712702</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27.1370408253621</t>
+          <t>522.276010769786</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.5159153924822</t>
+          <t>473.331232774438</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>32.1646826403424</t>
+          <t>492.608981271602</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>34.518468120635</t>
+          <t>503.383666989443</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>38.431975719047</t>
+          <t>487.540276644733</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>38.008361220193</t>
+          <t>505.608655745713</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.5839042490637</t>
+          <t>518.037625989418</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28.1610815462506</t>
+          <t>573.105195438213</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25.6476028977032</t>
+          <t>626.31319953977</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>23.9291690489315</t>
+          <t>654.741164194598</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>22.5580866760044</t>
+          <t>632.231850343409</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>20.2224473160373</t>
+          <t>644.420819586558</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16.9492103310518</t>
+          <t>674.306654734688</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>18.9405056976826</t>
+          <t>591.852957395148</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-507305506.076108</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-238713812.81731</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-405609824.441161</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-369592975.318576</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-371077388.469399</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-444269985.156602</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-89998993.6198646</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>187273217.511684</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>486103730.381795</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1141560707.50623</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1309941394.871</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>1425737166.91292</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1880220162.9487</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>2242599021.07384</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1882857653.36158</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-600230899.813379</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-366880464.232365</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>-468980445.399589</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-425343894.208989</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>-332503729.990507</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-408464593.553298</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-95316978.0040608</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>306026861.530327</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>572461598.749183</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1329897330.60412</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>1454048738.07344</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1613414370.78873</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>2042791790.72714</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2414575278.18852</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>2122209868.8759</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>92925393.7372711</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>128166651.415055</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>63370620.9584279</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>55750918.890413</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>-38573658.4788921</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>-35805391.6033045</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>5317984.38419621</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>-118753644.018644</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-86357868.3673883</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>-188336623.097893</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>-144107343.202443</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>-187677203.875806</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>-162571627.778435</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-171976257.11468</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-239352215.514319</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1934.70397039557</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>1932.76681223257</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1933.98452059255</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>1938.39065429296</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>1983.56923205922</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1982.54364395157</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>1881.98533806614</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>1852.87691525912</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1848.38490824424</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>1865.28944101795</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>1881.77990471389</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>1882.50669371392</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>1876.41992213971</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>1881.20873012761</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>1881.29140435433</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2017.27409561618</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2014.71657102644</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2018.61434067942</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2024.52556624705</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2057.64090234071</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2055.95872289702</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1964.94392563475</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1943.60764029914</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1945.48980531116</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1953.61502202972</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1965.07545248855</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>1960.28174217918</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>1947.82267450764</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>1955.65622553688</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1931.15104639132</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>201.6</t>
+          <t>25501.3563594792</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>27102.9554159455</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>135.4</t>
+          <t>26967.1371907302</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>129.19</t>
+          <t>30641.1681971173</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>129.62</t>
+          <t>30919.5145284852</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>139.14</t>
+          <t>33723.8702890759</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>115.61</t>
+          <t>37945.0674542685</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>108.01</t>
+          <t>43184.0017447542</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>107.99</t>
+          <t>53603.6437525298</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>73695.6695227233</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>85928.973087765</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>74.63</t>
+          <t>103876.178880117</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>133682.141617661</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>69.26</t>
+          <t>160845.920703747</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>121602.409514283</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>460.27</t>
+          <t>2635015980.69435</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>297.38</t>
+          <t>2486637186.86136</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>338.54</t>
+          <t>2664851996.37332</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>321.83</t>
+          <t>2799395559.34377</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>324.74</t>
+          <t>2914345224.8096</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>340.27</t>
+          <t>3062039339.3913</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>305.83</t>
+          <t>3159016643.57003</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>292.59</t>
+          <t>3202202781.91893</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>254.93</t>
+          <t>3377743286.52469</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>230.94</t>
+          <t>3876816446.79603</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>220.91</t>
+          <t>4185005063.13515</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>233.88</t>
+          <t>4581930422.53038</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>227.72</t>
+          <t>5124439346.76782</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>213.69</t>
+          <t>5442930184.45233</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>4366403057.65201</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>675.82</t>
+          <t>27596.0165001215</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>449.59</t>
+          <t>30603.8070708168</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>507.82</t>
+          <t>29732.2202731308</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>482.49</t>
+          <t>31512.8098103974</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>484.94</t>
+          <t>31669.8019193873</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>493.86</t>
+          <t>35362.2127479322</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>460.14</t>
+          <t>39436.9402112373</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>424.92</t>
+          <t>44180.7672190162</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>231.23</t>
+          <t>54904.7753543763</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>342.96</t>
+          <t>72308.1610802052</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>328.31</t>
+          <t>81433.6111258701</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>345.22</t>
+          <t>98543.6789830382</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>312.07</t>
+          <t>123846.643864586</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>284.41</t>
+          <t>149210.147984136</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>349.8</t>
+          <t>110242.021836695</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10385.389</t>
+          <t>2416394913.85015</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10466.783</t>
+          <t>2710695465.45033</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10506.601</t>
+          <t>2593838942.25841</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10374.742</t>
+          <t>2541681583.01589</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10183.985</t>
+          <t>2641835662.63735</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10157.388</t>
+          <t>2835699717.87776</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9751.944</t>
+          <t>3278102694.53646</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9700.054</t>
+          <t>3527622316.75983</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9578.514</t>
+          <t>4035172338.83611</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9651.583</t>
+          <t>4850354719.0279</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9808.906</t>
+          <t>4990782849.95318</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9974.58</t>
+          <t>5460672456.49141</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10175.114</t>
+          <t>6111725012.47015</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10460.522</t>
+          <t>6734500069.33761</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10103.591</t>
+          <t>5226692528.31886</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8581.482</t>
+          <t>-2094.66014064229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8594.152</t>
+          <t>-3500.85165487135</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8546.09</t>
+          <t>-2765.08308240057</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8336.71</t>
+          <t>-871.641613280143</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8137.807</t>
+          <t>-750.287390902122</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8094.805</t>
+          <t>-1638.34245885631</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7714.352</t>
+          <t>-1491.87275696879</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7569.647</t>
+          <t>-996.765474261954</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7358.729</t>
+          <t>-1301.13160184649</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7481.786</t>
+          <t>1387.50844251806</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7685.812</t>
+          <t>4495.36196189493</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7832.395</t>
+          <t>5332.49989707869</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8030.064</t>
+          <t>9835.49775307494</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>8156.526</t>
+          <t>11635.7727196113</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8002.884</t>
+          <t>11360.3876775878</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11896.829</t>
+          <t>218621066.844197</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12008.962</t>
+          <t>-224058278.588963</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12059.733</t>
+          <t>71013054.1149091</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11871.526</t>
+          <t>257713976.327884</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11452.829</t>
+          <t>272509562.172254</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11082.359</t>
+          <t>226339621.513544</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11206.42</t>
+          <t>-119086050.966434</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11304.352</t>
+          <t>-325419534.840902</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11288.293</t>
+          <t>-657429052.311415</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>11637.768</t>
+          <t>-973538272.231873</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11690.998</t>
+          <t>-805777786.818032</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12611.502</t>
+          <t>-878742033.961034</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>13135.859</t>
+          <t>-987285665.702335</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>13778.288</t>
+          <t>-1291569884.88527</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11525.256</t>
+          <t>-860289470.666844</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>27878.01033</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>32918.62252</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>29808.81218</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>31349.72661</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>29897.70559</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>27530.30469</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>30235.26834</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>36643.67487</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>43725.62879</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>54007.07428</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>59661.11896</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>69554.79096</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>84239.06212</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>103702.84821</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>89365.7284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6402.617</t>
+          <t>0.114907129213344</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6485.192</t>
+          <t>0.0889189321473404</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6446.657</t>
+          <t>0.0867197489244319</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6325.73</t>
+          <t>0.0966111013737814</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6085.864</t>
+          <t>0.101142310389155</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5991.293</t>
+          <t>0.101672580595399</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5756.066</t>
+          <t>0.103328361685593</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5659.98</t>
+          <t>0.10371574485157</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5538.096</t>
+          <t>0.10333620666329</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5558.336</t>
+          <t>0.110403635446004</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5618.71</t>
+          <t>0.114588134315015</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5689.107</t>
+          <t>0.12413770360883</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5779.303</t>
+          <t>0.132148813592566</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5903.721</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5565.062</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>18220.6268033519</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>27187.0100592577</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>25267.2653929607</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>26126.5752365978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>25163.5732089882</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>23884.7725715342</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>26170.0574150603</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>32666.5579290532</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>40090.0440019927</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>46874.1269933221</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>53686.4442984798</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>61450.9121663255</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>74981.2805796816</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>95746.3264610447</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>83007.720834956</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1642.916</t>
+          <t>21775.8771342148</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2322.328</t>
+          <t>32631.1792220981</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2091.605</t>
+          <t>30678.5639491407</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2118.633</t>
+          <t>32059.7484407347</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2065.186</t>
+          <t>30953.1831688823</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1990.646</t>
+          <t>29538.7840449964</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2072.515</t>
+          <t>32567.5223859693</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2116.364</t>
+          <t>41127.6238857033</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2281.627</t>
+          <t>51135.9488229703</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2512.179</t>
+          <t>59309.022845279</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2674.18</t>
+          <t>67189.3686554274</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2630.476</t>
+          <t>76949.7458276835</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2757.773</t>
+          <t>93596.0911283756</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2923.652</t>
+          <t>119867.694073496</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2517.702</t>
+          <t>103968.870192087</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>422.33</t>
+          <t>245498.944834045</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>270.07</t>
+          <t>262404.984455268</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>308.59</t>
+          <t>246863.545920945</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>293.49</t>
+          <t>251535.982032188</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>294.05</t>
+          <t>232354.061230121</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>306.64</t>
+          <t>217074.06555197</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>272.22</t>
+          <t>227769.80376059</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>257.67</t>
+          <t>266309.526907654</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>222.52</t>
+          <t>310306.857222978</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>197.82</t>
+          <t>356175.937376202</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>187.41</t>
+          <t>389305.140198336</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>197.76</t>
+          <t>418461.297431486</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>191.18</t>
+          <t>480946.802273826</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>178.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>217.86</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>21775.8771342148</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.778</t>
+          <t>30143.056266772</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>30562.7547582315</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.791</t>
+          <t>29723.8298489291</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.838</t>
+          <t>30221.9533004683</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.841</t>
+          <t>31252.5152808888</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.621</t>
+          <t>32282.2501246377</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.262</t>
+          <t>33807.7953334713</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.836</t>
+          <t>35840.1826172663</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>37028.468444557</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>39734.8868380869</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>42832.1023575882</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>45701.8534384225</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>49687.8598339644</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>45845.1677299452</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>18220.6268033519</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>25017.9801352588</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>24997.9531794996</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>23988.5354534885</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>24331.4543688855</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>25213.3004591456</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25830.5575065606</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>26885.4825903074</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>28019.7303953848</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>29184.5585467041</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>31791.5898054579</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>34430.0084207251</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>37081.9917019284</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>40513.2280366051</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>37041.6996023775</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>28209.5789757852</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>23332.7710079019</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>21407.9447208593</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>24301.1682592653</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>23500.8265811177</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>22070.4804250036</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>23535.0806640307</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>27620.4909442967</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>32065.9335270297</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>39323.118344721</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>44609.7496945726</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>51946.8245123165</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>63556.5493216244</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>77584.1123065039</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>67265.4924279131</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8581482000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8594152000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>8546090000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8336710000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8137807000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8094805000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7714352000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7569647000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7358729000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>7481786000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7685812000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7832395000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8030064000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>8156526000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>8002883825.01644</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10385389000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10466783000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10506601000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10374742000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10183985000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10157388000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9751944000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9700054000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9578514000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9651583000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9808906000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9974580000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10175114000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10460522320.2866</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10103590571.8892</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6402617000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6485192000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6446657000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6325730000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6085864000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5991293000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5756066000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5659980000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5538096000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5558336000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5618710000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5689107000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5779303000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5903721098.81198</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5565061504.42354</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5148229</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5195164</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5204858</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5124530</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4949350</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4940463</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4962963</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4990747</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4923446</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4940371</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4991618</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5088340</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5223840</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5348855.37841137</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5231900.73131227</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4435553</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4446554</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4418903</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4300841</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4102608</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4083040</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4099050</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4085348</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3981167</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4011059</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4084331</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4160620</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4279460</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4335790</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4253931</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10385389000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10466783000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10506601000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10374742000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10183985000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10157388000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9751944000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9700054000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9578514000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9651583000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9808906000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9974580000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10175114000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10460522320.2866</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10103590571.8892</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>8581482000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8594152000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8546090000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8336710000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8137807000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8094805000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7714352000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7569647000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7358729000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7481786000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7685812000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7832395000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>8030064000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>8156526000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8002883825.01644</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.169692810054207</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.174571254618226</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.180603645253425</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.183167233522844</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.164338498629227</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.196551407834206</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.199010445363947</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.204605442127207</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.204820376511823</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207445680303656</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.22328919934111</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.764606255087522</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.761221530850925</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.759783404645724</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.758548259103415</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.755796073865582</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.753244363573396</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.754922311106197</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.749235944721564</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.745383539411571</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.742689920171966</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.730952614362941</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0657009348582706</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0642072145308483</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0596129501008513</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0582845073737414</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0798654275051914</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0502042285923985</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0460672435298555</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0461586131512284</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0497960840766058</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0498643995243779</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0457581862959489</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.102469307678463</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.1048336444026</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.107287624360311</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.11085272498633</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.111754106723243</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.118224859000065</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.120142272903144</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.123403193107016</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.123442430242449</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.130484887563702</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.14159480219758</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.804787187220306</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.806229363696137</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.808486122329607</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.809789865320462</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.813629861056625</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.813023399505688</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.816831842181587</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.81329555491645</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.81212231911831</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.806522264713003</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.799894088103586</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0927435051012311</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0889369919012627</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0842262533100811</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.079357409693207</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0746160322201317</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0687517414942476</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0630258849152691</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0633012519765343</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0644352506392414</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.062992847723295</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0585111096988344</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>131930.33656</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>145588.42367</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>138889.0318</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>148099.64303</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>141552.28303</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>139960.6931</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>154545.02045</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>185157.89271</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>226745.6239</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>275233.32295</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>310792.53065</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>368770.01749</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>456657.19042</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>564946.54779</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>458086.21635</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>49985.45611</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>55963.95023</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>52086.50867</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>56360.9167</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>54454.00975</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>51609.26447</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>56102.60305</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>68748.11483</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>83201.88235</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>98632.14119</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>111799.11835</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>128896.57034</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>157152.64045</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>197451.80638</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>171234.36262</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6513636.35600347</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6732155.90104509</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6916439.49357942</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>7098294.2932243</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>7283933.21595949</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7494372.74102545</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7750162.13301742</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7975477.2427386</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>8180646.87159439</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>8397388.0706155</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8599857.0472584</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8854511.26223221</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>9152706.06043163</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
